--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N67_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0003T0006Z000C1N67_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.47086716790206</v>
+        <v>4.789015914784084</v>
       </c>
       <c r="D2" t="n">
-        <v>29.26748609006425</v>
+        <v>4.75596648963544</v>
       </c>
       <c r="E2" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F2" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.91870375914763</v>
+        <v>3.56178936086149</v>
       </c>
       <c r="D3" t="n">
-        <v>21.38775881593896</v>
+        <v>3.475510807590081</v>
       </c>
       <c r="E3" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F3" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.87948575743105</v>
+        <v>2.417916435582546</v>
       </c>
       <c r="D4" t="n">
-        <v>14.60671820540659</v>
+        <v>2.373591708378571</v>
       </c>
       <c r="E4" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F4" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.91202946670212</v>
+        <v>4.698204788339095</v>
       </c>
       <c r="D5" t="n">
-        <v>29.05789313285093</v>
+        <v>4.721907634088277</v>
       </c>
       <c r="E5" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F5" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.22095512926109</v>
+        <v>4.260905208504927</v>
       </c>
       <c r="D6" t="n">
-        <v>26.06246482155472</v>
+        <v>4.235150533502642</v>
       </c>
       <c r="E6" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F6" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.91620681563099</v>
+        <v>3.723883607540036</v>
       </c>
       <c r="D7" t="n">
-        <v>23.21236504020781</v>
+        <v>3.772009319033769</v>
       </c>
       <c r="E7" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F7" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.09243148958993</v>
+        <v>2.940020117058364</v>
       </c>
       <c r="D8" t="n">
-        <v>18.51888571458574</v>
+        <v>3.009318928620182</v>
       </c>
       <c r="E8" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F8" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>10.68760591755291</v>
+        <v>1.736735961602347</v>
       </c>
       <c r="D9" t="n">
-        <v>11.01471436269386</v>
+        <v>1.789891083937753</v>
       </c>
       <c r="E9" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F9" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.27228589539447</v>
+        <v>5.244246458001601</v>
       </c>
       <c r="D10" t="n">
-        <v>32.01418010534485</v>
+        <v>5.202304267118538</v>
       </c>
       <c r="E10" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F10" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>5.363428626752891</v>
+        <v>0.8715571518473448</v>
       </c>
       <c r="D11" t="n">
-        <v>5.018318537941514</v>
+        <v>0.815476762415496</v>
       </c>
       <c r="E11" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F11" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.74816287887576</v>
+        <v>4.346576467817311</v>
       </c>
       <c r="D12" t="n">
-        <v>27.60598529564194</v>
+        <v>4.485972610541815</v>
       </c>
       <c r="E12" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F12" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>23.45620247493812</v>
+        <v>3.811632902177445</v>
       </c>
       <c r="D13" t="n">
-        <v>22.84931186791813</v>
+        <v>3.713013178536695</v>
       </c>
       <c r="E13" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F13" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>8.144066621439562</v>
+        <v>1.323410825983929</v>
       </c>
       <c r="D14" t="n">
-        <v>8.397554938407882</v>
+        <v>1.364602677491281</v>
       </c>
       <c r="E14" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F14" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>20.68699955463342</v>
+        <v>3.361637427627931</v>
       </c>
       <c r="D15" t="n">
-        <v>21.55317509491795</v>
+        <v>3.502390952924168</v>
       </c>
       <c r="E15" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F15" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>21.68187184802085</v>
+        <v>3.523304175303389</v>
       </c>
       <c r="D16" t="n">
-        <v>21.44986497744368</v>
+        <v>3.485603058834599</v>
       </c>
       <c r="E16" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F16" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>11.18514502246577</v>
+        <v>1.817586066150687</v>
       </c>
       <c r="D17" t="n">
-        <v>10.36312454975833</v>
+        <v>1.684007739335728</v>
       </c>
       <c r="E17" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F17" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>16.47681500484162</v>
+        <v>2.677482438286764</v>
       </c>
       <c r="D18" t="n">
-        <v>16.9340380527873</v>
+        <v>2.751781183577937</v>
       </c>
       <c r="E18" t="n">
-        <v>7.642143432776271</v>
+        <v>1.241848307826144</v>
       </c>
       <c r="F18" t="n">
-        <v>7.689109173930112</v>
+        <v>1.249480240763643</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
